--- a/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
+++ b/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
@@ -799,13 +799,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45163.60853558977</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45214</v>
+      </c>
+    </row>
     <row r="6" ht="8.25" customHeight="1" s="24"/>
     <row r="7" ht="19.5" customHeight="1" s="24">
       <c r="A7" s="17" t="inlineStr">
@@ -817,7 +813,6 @@
     <row r="8" ht="20.25" customHeight="1" s="24">
       <c r="A8" s="16" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="41.25" customHeight="1" s="24">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -877,7 +872,6 @@
       <c r="D19" s="4" t="n"/>
       <c r="F19" s="5" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21" ht="15" customHeight="1" s="24">
       <c r="A21" s="20" t="inlineStr">
         <is>
@@ -909,7 +903,7 @@
       </c>
       <c r="C22" s="19" t="n"/>
       <c r="D22" s="11" t="n">
-        <v>74.125</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="23" ht="12" customHeight="1" s="24">
@@ -934,15 +928,6 @@
     <row r="26" ht="18" customHeight="1" s="24">
       <c r="D26" s="4" t="n"/>
     </row>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36" ht="15" customHeight="1" s="24">
       <c r="A36" s="21" t="inlineStr">
         <is>
@@ -974,14 +959,12 @@
       </c>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="11" t="n">
-        <v>81.5</v>
-      </c>
-    </row>
-    <row r="38"/>
+        <v>85.5</v>
+      </c>
+    </row>
     <row r="39" ht="18" customHeight="1" s="24">
       <c r="A39" s="10" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41" ht="15" customHeight="1" s="24">
       <c r="A41" s="8" t="n"/>
       <c r="D41" s="9" t="n"/>
@@ -996,17 +979,16 @@
       <c r="D42" s="4" t="n"/>
       <c r="F42" s="5" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="15" customHeight="1" s="24">
       <c r="A44" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
+++ b/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
@@ -799,7 +799,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45214</v>
+        <v>45223</v>
       </c>
     </row>
     <row r="6" ht="8.25" customHeight="1" s="24"/>
@@ -984,10 +984,10 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>

--- a/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
+++ b/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
@@ -799,7 +799,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45223</v>
+        <v>45232</v>
       </c>
     </row>
     <row r="6" ht="8.25" customHeight="1" s="24"/>
@@ -984,11 +984,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
+++ b/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
@@ -799,7 +799,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45232</v>
+        <v>45237</v>
       </c>
     </row>
     <row r="6" ht="8.25" customHeight="1" s="24"/>

--- a/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
+++ b/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
@@ -799,7 +799,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
     </row>
     <row r="6" ht="8.25" customHeight="1" s="24"/>
@@ -984,11 +984,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
+++ b/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
@@ -799,7 +799,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45238</v>
+        <v>45244</v>
       </c>
     </row>
     <row r="6" ht="8.25" customHeight="1" s="24"/>

--- a/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
+++ b/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
@@ -799,7 +799,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45244</v>
+        <v>45253</v>
       </c>
     </row>
     <row r="6" ht="8.25" customHeight="1" s="24"/>

--- a/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
+++ b/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
@@ -799,7 +799,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
     </row>
     <row r="6" ht="8.25" customHeight="1" s="24"/>
@@ -984,11 +984,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
+++ b/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
@@ -799,7 +799,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="6" ht="8.25" customHeight="1" s="24"/>

--- a/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
+++ b/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
@@ -799,9 +799,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45266</v>
-      </c>
-    </row>
+        <v>45258.54557503269</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="8.25" customHeight="1" s="24"/>
     <row r="7" ht="19.5" customHeight="1" s="24">
       <c r="A7" s="17" t="inlineStr">
@@ -813,6 +817,7 @@
     <row r="8" ht="20.25" customHeight="1" s="24">
       <c r="A8" s="16" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="41.25" customHeight="1" s="24">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -872,6 +877,7 @@
       <c r="D19" s="4" t="n"/>
       <c r="F19" s="5" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21" ht="15" customHeight="1" s="24">
       <c r="A21" s="20" t="inlineStr">
         <is>
@@ -903,7 +909,7 @@
       </c>
       <c r="C22" s="19" t="n"/>
       <c r="D22" s="11" t="n">
-        <v>77.8</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="23" ht="12" customHeight="1" s="24">
@@ -928,6 +934,15 @@
     <row r="26" ht="18" customHeight="1" s="24">
       <c r="D26" s="4" t="n"/>
     </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
     <row r="36" ht="15" customHeight="1" s="24">
       <c r="A36" s="21" t="inlineStr">
         <is>
@@ -959,12 +974,14 @@
       </c>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="11" t="n">
-        <v>85.5</v>
-      </c>
-    </row>
+        <v>156.8</v>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39" ht="18" customHeight="1" s="24">
       <c r="A39" s="10" t="n"/>
     </row>
+    <row r="40"/>
     <row r="41" ht="15" customHeight="1" s="24">
       <c r="A41" s="8" t="n"/>
       <c r="D41" s="9" t="n"/>
@@ -979,16 +996,17 @@
       <c r="D42" s="4" t="n"/>
       <c r="F42" s="5" t="n"/>
     </row>
+    <row r="43"/>
     <row r="44" ht="15" customHeight="1" s="24">
       <c r="A44" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
+++ b/LISTAS/ma/CABLE ACERO Y ALAMBRE ROPA.xlsx
@@ -799,13 +799,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45258.54557503269</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45286</v>
+      </c>
+    </row>
     <row r="6" ht="8.25" customHeight="1" s="24"/>
     <row r="7" ht="19.5" customHeight="1" s="24">
       <c r="A7" s="17" t="inlineStr">
@@ -817,7 +813,6 @@
     <row r="8" ht="20.25" customHeight="1" s="24">
       <c r="A8" s="16" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="41.25" customHeight="1" s="24">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -877,7 +872,6 @@
       <c r="D19" s="4" t="n"/>
       <c r="F19" s="5" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21" ht="15" customHeight="1" s="24">
       <c r="A21" s="20" t="inlineStr">
         <is>
@@ -909,7 +903,7 @@
       </c>
       <c r="C22" s="19" t="n"/>
       <c r="D22" s="11" t="n">
-        <v>112.2</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="23" ht="12" customHeight="1" s="24">
@@ -934,15 +928,6 @@
     <row r="26" ht="18" customHeight="1" s="24">
       <c r="D26" s="4" t="n"/>
     </row>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36" ht="15" customHeight="1" s="24">
       <c r="A36" s="21" t="inlineStr">
         <is>
@@ -974,14 +959,12 @@
       </c>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="11" t="n">
-        <v>156.8</v>
-      </c>
-    </row>
-    <row r="38"/>
+        <v>85.5</v>
+      </c>
+    </row>
     <row r="39" ht="18" customHeight="1" s="24">
       <c r="A39" s="10" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41" ht="15" customHeight="1" s="24">
       <c r="A41" s="8" t="n"/>
       <c r="D41" s="9" t="n"/>
@@ -996,17 +979,16 @@
       <c r="D42" s="4" t="n"/>
       <c r="F42" s="5" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="15" customHeight="1" s="24">
       <c r="A44" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
